--- a/MM_26 Bill of Parts.xlsx
+++ b/MM_26 Bill of Parts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\Documents\Github\Micromouse-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF54DA1-315E-46AB-93DE-D8419E59A623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C97AF22-4433-4F34-8F8B-7BD43C3B7F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C0469B51-F70B-4F72-8A5A-A226DBC3104A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>Part</t>
   </si>
@@ -153,6 +153,30 @@
   </si>
   <si>
     <t>Gryo + Accel</t>
+  </si>
+  <si>
+    <t>Battery Connector</t>
+  </si>
+  <si>
+    <t>2mm JST Connector</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/jst-sales-america-inc/B2B-PH-K-S-LF-SN/926611</t>
+  </si>
+  <si>
+    <t>455-1704-ND</t>
+  </si>
+  <si>
+    <t>Slide Switch</t>
+  </si>
+  <si>
+    <t>563-1314-1-ND</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/nidec-components-corporation/CL-SB-12A-01T/3507814</t>
+  </si>
+  <si>
+    <t>Switch</t>
   </si>
 </sst>
 </file>
@@ -562,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D335EDAF-01BC-43D0-BDFE-27332DC556ED}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" bestFit="1" customWidth="1"/>
@@ -846,6 +870,46 @@
         <v>30</v>
       </c>
     </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" t="s">
+        <v>40</v>
+      </c>
+      <c r="I12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" t="s">
+        <v>46</v>
+      </c>
+      <c r="I13" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I3" r:id="rId1" xr:uid="{87E20980-8068-41A3-A2DD-B64AA5CD53A2}"/>

--- a/MM_26 Bill of Parts.xlsx
+++ b/MM_26 Bill of Parts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\Documents\Github\Micromouse-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C97AF22-4433-4F34-8F8B-7BD43C3B7F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F1249E-3413-4C69-BD34-E7F842BC1DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C0469B51-F70B-4F72-8A5A-A226DBC3104A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>Part</t>
   </si>
@@ -143,15 +143,9 @@
     <t>STM32 Nucleo L476RG</t>
   </si>
   <si>
-    <t>https://www.adafruit.com/product/3948</t>
-  </si>
-  <si>
     <t>Display</t>
   </si>
   <si>
-    <t>Free spinning wheel</t>
-  </si>
-  <si>
     <t>Gryo + Accel</t>
   </si>
   <si>
@@ -177,6 +171,45 @@
   </si>
   <si>
     <t>Switch</t>
+  </si>
+  <si>
+    <t>JST SH Connector</t>
+  </si>
+  <si>
+    <t>Motor to Board</t>
+  </si>
+  <si>
+    <t>www.digikey.com/en/products/detail/jst-sales-america-inc/BM06B-SRSS-TB/926698</t>
+  </si>
+  <si>
+    <t>455-BM06B-SRSS-TBCT-ND</t>
+  </si>
+  <si>
+    <t>Motor Cable</t>
+  </si>
+  <si>
+    <t>https://www.pololu.com/category/277/6-pin-jst-sh-style-cables-for-micro-metal-gearmotor-encoders</t>
+  </si>
+  <si>
+    <t>Decide Length</t>
+  </si>
+  <si>
+    <t>https://www.pololu.com/category/45/pololu-ball-casters</t>
+  </si>
+  <si>
+    <t>Decide based on height</t>
+  </si>
+  <si>
+    <t>https://amazon.com/dp/B07W97H2WS</t>
+  </si>
+  <si>
+    <t>Right Angle Pin Header</t>
+  </si>
+  <si>
+    <t>For IR Sensor Module</t>
+  </si>
+  <si>
+    <t>https://www.pololu.com/product/2703</t>
   </si>
 </sst>
 </file>
@@ -238,7 +271,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
@@ -250,6 +283,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="fill"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -586,10 +623,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D335EDAF-01BC-43D0-BDFE-27332DC556ED}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.08984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
@@ -676,7 +713,7 @@
         <v>12</v>
       </c>
       <c r="H3" s="1">
-        <f t="shared" ref="H3:H4" si="0">(B3+C3)*D3</f>
+        <f t="shared" ref="H3:H5" si="0">(B3+C3)*D3</f>
         <v>7.95</v>
       </c>
       <c r="I3" s="6" t="s">
@@ -718,7 +755,23 @@
       <c r="B5">
         <v>5</v>
       </c>
-      <c r="D5" s="1"/>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.879</v>
+      </c>
+      <c r="F5" s="2" t="str">
+        <f>HYPERLINK(I5)</f>
+        <v>https://amazon.com/dp/B07W97H2WS</v>
+      </c>
+      <c r="H5" s="1">
+        <f t="shared" si="0"/>
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="I5" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
@@ -734,7 +787,7 @@
         <v>20</v>
       </c>
       <c r="F6" s="2" t="str">
-        <f t="shared" ref="F6:F11" si="1">HYPERLINK(I6)</f>
+        <f t="shared" ref="F6:F14" si="1">HYPERLINK(I6)</f>
         <v>https://www.digikey.com/en/products/detail/stmicroelectronics/L293DD/585913</v>
       </c>
       <c r="G6" t="s">
@@ -766,7 +819,7 @@
         <v>https://www.adafruit.com/product/4502</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" si="2"/>
@@ -805,21 +858,16 @@
       <c r="A9" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="1">
-        <v>1.95</v>
-      </c>
-      <c r="E9">
-        <v>3948</v>
-      </c>
-      <c r="F9" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>https://www.adafruit.com/product/3948</v>
-      </c>
-      <c r="G9" t="s">
-        <v>37</v>
-      </c>
+      <c r="C9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
       <c r="I9" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -840,7 +888,7 @@
         <v>https://www.adafruit.com/product/661</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I10" t="s">
         <v>28</v>
@@ -872,7 +920,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -881,18 +929,22 @@
         <v>0.1</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="F12" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.digikey.com/en/products/detail/jst-sales-america-inc/B2B-PH-K-S-LF-SN/926611</v>
       </c>
       <c r="G12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -901,16 +953,85 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="E13" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.digikey.com/en/products/detail/nidec-components-corporation/CL-SB-12A-01T/3507814</v>
+      </c>
+      <c r="G13" t="s">
         <v>44</v>
       </c>
-      <c r="G13" t="s">
+      <c r="I13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="E14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>www.digikey.com/en/products/detail/jst-sales-america-inc/BM06B-SRSS-TB/926698</v>
+      </c>
+      <c r="G14" t="s">
         <v>46</v>
       </c>
-      <c r="I13" t="s">
-        <v>45</v>
+      <c r="I14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0.52</v>
+      </c>
+      <c r="E16">
+        <v>2703</v>
+      </c>
+      <c r="G16" t="s">
+        <v>56</v>
+      </c>
+      <c r="I16" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="C9:H9"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink ref="I3" r:id="rId1" xr:uid="{87E20980-8068-41A3-A2DD-B64AA5CD53A2}"/>
     <hyperlink ref="I6" r:id="rId2" xr:uid="{7F8DDEFE-77E5-427E-893F-2E1CCB9012D5}"/>

--- a/MM_26 Bill of Parts.xlsx
+++ b/MM_26 Bill of Parts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\Documents\Github\Micromouse-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F1249E-3413-4C69-BD34-E7F842BC1DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDC6FF0-58E3-436B-BF66-F352A6D162A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C0469B51-F70B-4F72-8A5A-A226DBC3104A}"/>
   </bookViews>
@@ -271,7 +271,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
@@ -286,7 +286,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1014,7 +1013,7 @@
       <c r="B16">
         <v>5</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="1">
         <v>0.52</v>
       </c>
       <c r="E16">

--- a/MM_26 Bill of Parts.xlsx
+++ b/MM_26 Bill of Parts.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\Documents\Github\Micromouse-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDC6FF0-58E3-436B-BF66-F352A6D162A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10286D8-F4A4-491D-810C-E0B2C1B83B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C0469B51-F70B-4F72-8A5A-A226DBC3104A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>Part</t>
   </si>
@@ -210,6 +210,12 @@
   </si>
   <si>
     <t>https://www.pololu.com/product/2703</t>
+  </si>
+  <si>
+    <t>Motor Bracket</t>
+  </si>
+  <si>
+    <t>https://www.pololu.com/category/161/brackets-for-micro-metal-gearmotors</t>
   </si>
 </sst>
 </file>
@@ -622,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D335EDAF-01BC-43D0-BDFE-27332DC556ED}">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.08984375" bestFit="1" customWidth="1"/>
@@ -1026,6 +1032,23 @@
         <v>57</v>
       </c>
     </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1">
+        <v>4.95</v>
+      </c>
+      <c r="E17">
+        <v>1089</v>
+      </c>
+      <c r="F17" t="s">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B15:H15"/>

--- a/MM_26 Bill of Parts.xlsx
+++ b/MM_26 Bill of Parts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\Documents\Github\Micromouse-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10286D8-F4A4-491D-810C-E0B2C1B83B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A7F675-2F06-44A7-9AF4-E689DB5E8125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C0469B51-F70B-4F72-8A5A-A226DBC3104A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
   <si>
     <t>Part</t>
   </si>
@@ -164,12 +164,6 @@
     <t>Slide Switch</t>
   </si>
   <si>
-    <t>563-1314-1-ND</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/nidec-components-corporation/CL-SB-12A-01T/3507814</t>
-  </si>
-  <si>
     <t>Switch</t>
   </si>
   <si>
@@ -216,6 +210,72 @@
   </si>
   <si>
     <t>https://www.pololu.com/category/161/brackets-for-micro-metal-gearmotors</t>
+  </si>
+  <si>
+    <t>Resistor</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/RC0805JR-0710KL/728241</t>
+  </si>
+  <si>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>4.7uF</t>
+  </si>
+  <si>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>22uF</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/kemet/C0805C104K5RACTU/411169</t>
+  </si>
+  <si>
+    <t>399-C0805C104K5RACTUCT-ND</t>
+  </si>
+  <si>
+    <t>1276-1244-1-ND</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/samsung-electro-mechanics/CL21A475KAQNNNE/3886902</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/samsung-electro-mechanics/CL21B106KOQNNNE/3888530</t>
+  </si>
+  <si>
+    <t>1276-2872-1-ND</t>
+  </si>
+  <si>
+    <t>1276-CL21A226MAYNNNECT-ND</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/samsung-electro-mechanics/CL21A226MAYNNNE/10479857</t>
+  </si>
+  <si>
+    <t>IDC Cable Header</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/cnc-tech/3220-20-0100-00/3883663</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/samtec-inc/FFSD-10-D-02-00-01-N/1106582</t>
+  </si>
+  <si>
+    <t>Cable Long</t>
+  </si>
+  <si>
+    <t>Cable Short</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/samtec-inc/FFSD-10-D-03-00-01-N/2651117</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/e-switch/EG1213/101735</t>
+  </si>
+  <si>
+    <t>EG1906-ND</t>
   </si>
 </sst>
 </file>
@@ -628,7 +688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D335EDAF-01BC-43D0-BDFE-27332DC556ED}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.08984375" bestFit="1" customWidth="1"/>
@@ -775,7 +835,7 @@
         <v>8.7899999999999991</v>
       </c>
       <c r="I5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -864,7 +924,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
@@ -872,7 +932,7 @@
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -952,28 +1012,31 @@
         <v>41</v>
       </c>
       <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>1.1000000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="F13" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>https://www.digikey.com/en/products/detail/nidec-components-corporation/CL-SB-12A-01T/3507814</v>
+        <v>https://www.digikey.com/en/products/detail/e-switch/EG1213/101735</v>
       </c>
       <c r="G13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I13" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B14">
         <v>2</v>
@@ -982,25 +1045,25 @@
         <v>0.67</v>
       </c>
       <c r="E14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F14" s="2" t="str">
         <f t="shared" si="1"/>
         <v>www.digikey.com/en/products/detail/jst-sales-america-inc/BM06B-SRSS-TB/926698</v>
       </c>
       <c r="G14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>49</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>51</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -1009,12 +1072,12 @@
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -1026,15 +1089,15 @@
         <v>2703</v>
       </c>
       <c r="G16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1046,7 +1109,92 @@
         <v>1089</v>
       </c>
       <c r="F17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>9</v>
+      </c>
+      <c r="D18" s="1">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="F18" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>76</v>
+      </c>
+      <c r="F24" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>75</v>
+      </c>
+      <c r="F25" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/MM_26 Bill of Parts.xlsx
+++ b/MM_26 Bill of Parts.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\Documents\Github\Micromouse-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A7F675-2F06-44A7-9AF4-E689DB5E8125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F77FF91-9609-4429-923E-3BC8C8493430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C0469B51-F70B-4F72-8A5A-A226DBC3104A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{C0469B51-F70B-4F72-8A5A-A226DBC3104A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="receipts" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="95">
   <si>
     <t>Part</t>
   </si>
@@ -276,6 +277,51 @@
   </si>
   <si>
     <t>EG1906-ND</t>
+  </si>
+  <si>
+    <t>DIGIKEY 1</t>
+  </si>
+  <si>
+    <t>DIGIKEY 2</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>ADAFRUIT</t>
+  </si>
+  <si>
+    <t>JLC</t>
+  </si>
+  <si>
+    <t>Receipt</t>
+  </si>
+  <si>
+    <t>AMAZON</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Materials to connect top and bottom board</t>
+  </si>
+  <si>
+    <t>Parts on boards</t>
+  </si>
+  <si>
+    <t>Gyroscope + OLED</t>
+  </si>
+  <si>
+    <t>POLOLU</t>
+  </si>
+  <si>
+    <t>Motors, Mechanical Assembly Parts</t>
+  </si>
+  <si>
+    <t>Batteries</t>
+  </si>
+  <si>
+    <t>PCBs</t>
   </si>
 </sst>
 </file>
@@ -1208,4 +1254,103 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2B56342-DD7E-4F8E-A3C8-E28CCCABB28A}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="35.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2">
+        <v>50.08</v>
+      </c>
+      <c r="D2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3">
+        <v>38.56</v>
+      </c>
+      <c r="D3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4">
+        <v>55.93</v>
+      </c>
+      <c r="D4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5">
+        <v>71.430000000000007</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6">
+        <v>113.18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="D7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8">
+        <f>SUM(B2:B7)</f>
+        <v>349.08</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>